--- a/output/2026-09-01_19_Italia_Marche_Cleaning.xlsx
+++ b/output/2026-09-01_19_Italia_Marche_Cleaning.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore materiale elettrico/industriale, rivenditore autorizzato Karcher.</t>
+          <t>Distributore materiale elettrico/industriale, rivenditore autorizzato Karcher. [DUPLICATO — vedi anche: 2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -578,10 +578,9 @@
           <t>0733 203205</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede legale RemaTarlazzi SPA, rivenditore Karcher. Email non reperita.</t>
+          <t>Sede legale RemaTarlazzi SPA, rivenditore Karcher. Email non reperita. [DUPLICATO — vedi anche: 2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,10 +615,9 @@
           <t>0721 23843</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Punto vendita storico Rema (dal 1974), rivenditore Karcher. Email non reperita.</t>
+          <t>Punto vendita storico Rema (dal 1974), rivenditore Karcher. Email non reperita. [DUPLICATO — vedi anche: 2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -691,8 +689,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Vendita/noleggio macchine pulizia professionale e prodotti chimici, oltre 40 anni attivita. Telefono/email non reperiti pubblicamente.</t>
@@ -814,7 +810,6 @@
           <t>0721 498517</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Progettazione/installazione impianti di aspirazione industriale (fumi, polveri, silos). Email di lista grezza scartata (dominio di terza azienda non collegata).</t>
@@ -894,7 +889,6 @@
           <t>0721 499043</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Bonifica ambienti di lavoro industriali, impianti di filtrazione/aspirazione aria, abbattimento polveri e rumore.</t>
@@ -927,11 +921,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sede legale reale a Paderno Ponchielli (CR), fuori regione Marche; copertura commerciale dichiarata su Ancona/Pesaro-Urbino tramite landing page dedicata, nessuna sede fisica in Marche confermata.</t>
+          <t>Sede legale reale a Paderno Ponchielli (CR), fuori regione Marche; copertura commerciale dichiarata su Ancona/Pesaro-Urbino tramite landing page dedicata, nessuna sede fisica in Marche confermata. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -966,10 +958,9 @@
           <t>0854 684090 / 348 7012722</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sede legale reale a Montesilvano (PE), fuori regione Marche; copertura commerciale dichiarata su Macerata/Fermo/Ascoli Piceno, nessuna sede fisica in Marche confermata.</t>
+          <t>Sede legale reale a Montesilvano (PE), fuori regione Marche; copertura commerciale dichiarata su Macerata/Fermo/Ascoli Piceno, nessuna sede fisica in Marche confermata. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
